--- a/artfynd/A 53600-2024 artfynd.xlsx
+++ b/artfynd/A 53600-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>80907075</v>
       </c>
       <c r="B2" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504808.0980370713</v>
+        <v>504808</v>
       </c>
       <c r="R2" t="n">
-        <v>6610422.722352162</v>
+        <v>6610423</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -762,19 +757,9 @@
           <t>2019-07-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -810,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93752936</v>
+        <v>93752935</v>
       </c>
       <c r="B3" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -864,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504805.5383569209</v>
+        <v>504785</v>
       </c>
       <c r="R3" t="n">
-        <v>6610443.454527387</v>
+        <v>6610470</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,19 +877,9 @@
           <t>2020-09-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -948,6 +918,266 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>93752936</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brännkorshagarna inklusive Bromsjö bodar Delyta 6:5, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>504806</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6610444</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>93752937</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brännkorshagarna inklusive Bromsjö bodar Delyta 6:5, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504824</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6610444</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-09-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
